--- a/artfynd/A 17953-2024 artfynd.xlsx
+++ b/artfynd/A 17953-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118318096</v>
+        <v>118318095</v>
       </c>
       <c r="B2" t="n">
-        <v>100017</v>
+        <v>103349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416909</v>
+        <v>416915</v>
       </c>
       <c r="R2" t="n">
-        <v>6613866</v>
+        <v>6613847</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118318095</v>
+        <v>118318096</v>
       </c>
       <c r="B3" t="n">
-        <v>103349</v>
+        <v>100017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416915</v>
+        <v>416909</v>
       </c>
       <c r="R3" t="n">
-        <v>6613847</v>
+        <v>6613866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118318101</v>
+        <v>118318097</v>
       </c>
       <c r="B4" t="n">
         <v>100017</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416860</v>
+        <v>416903</v>
       </c>
       <c r="R4" t="n">
-        <v>6614056</v>
+        <v>6613871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118318097</v>
+        <v>118318101</v>
       </c>
       <c r="B5" t="n">
         <v>100017</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416903</v>
+        <v>416860</v>
       </c>
       <c r="R5" t="n">
-        <v>6613871</v>
+        <v>6614056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 17953-2024 artfynd.xlsx
+++ b/artfynd/A 17953-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118318095</v>
+        <v>118318101</v>
       </c>
       <c r="B2" t="n">
-        <v>103349</v>
+        <v>100017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416915</v>
+        <v>416860</v>
       </c>
       <c r="R2" t="n">
-        <v>6613847</v>
+        <v>6614056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118318101</v>
+        <v>118318095</v>
       </c>
       <c r="B5" t="n">
-        <v>100017</v>
+        <v>103349</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416860</v>
+        <v>416915</v>
       </c>
       <c r="R5" t="n">
-        <v>6614056</v>
+        <v>6613847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 17953-2024 artfynd.xlsx
+++ b/artfynd/A 17953-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118318101</v>
       </c>
       <c r="B2" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118318096</v>
+        <v>118318095</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
+        <v>103356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416909</v>
+        <v>416915</v>
       </c>
       <c r="R3" t="n">
-        <v>6613866</v>
+        <v>6613847</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>118318097</v>
       </c>
       <c r="B4" t="n">
-        <v>100017</v>
+        <v>100024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118318095</v>
+        <v>118318096</v>
       </c>
       <c r="B5" t="n">
-        <v>103349</v>
+        <v>100024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416915</v>
+        <v>416909</v>
       </c>
       <c r="R5" t="n">
-        <v>6613847</v>
+        <v>6613866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
